--- a/ombreathe_config_template_new.xlsx
+++ b/ombreathe_config_template_new.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\pk\Baliyoga\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB9243A8-7CB1-4E9D-8D22-B79EAC85132A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BCC4B0D-3F65-403B-AD42-DD56A03932C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1604,12 +1604,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="34.296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1626,7 +1626,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1643,7 +1643,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1660,7 +1660,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1677,7 +1677,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1711,7 +1711,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1728,7 +1728,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -1762,7 +1762,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -1779,7 +1779,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -1830,7 +1830,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -1864,7 +1864,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -1881,7 +1881,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -1898,7 +1898,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -1915,7 +1915,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -1932,7 +1932,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>5</v>
       </c>
@@ -1949,7 +1949,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -1966,7 +1966,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>5</v>
       </c>
@@ -1983,7 +1983,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>5</v>
       </c>
@@ -2000,7 +2000,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>5</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>91</v>
       </c>
@@ -2034,7 +2034,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>91</v>
       </c>
@@ -2051,7 +2051,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>91</v>
       </c>
@@ -2068,7 +2068,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>91</v>
       </c>
@@ -2085,7 +2085,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>91</v>
       </c>
@@ -2102,7 +2102,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>91</v>
       </c>
@@ -2119,7 +2119,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>91</v>
       </c>
@@ -2136,7 +2136,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>91</v>
       </c>
@@ -2153,7 +2153,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>91</v>
       </c>
@@ -2170,7 +2170,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>91</v>
       </c>
@@ -2187,7 +2187,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>91</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>91</v>
       </c>
@@ -2221,7 +2221,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>91</v>
       </c>
@@ -2238,7 +2238,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>91</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>91</v>
       </c>
@@ -2272,7 +2272,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>91</v>
       </c>
@@ -2289,7 +2289,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>91</v>
       </c>
@@ -2306,7 +2306,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>91</v>
       </c>
@@ -2323,7 +2323,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>91</v>
       </c>
@@ -2340,7 +2340,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>91</v>
       </c>
@@ -2357,7 +2357,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>91</v>
       </c>
@@ -2374,7 +2374,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>91</v>
       </c>
@@ -2391,7 +2391,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>91</v>
       </c>
@@ -2408,7 +2408,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>91</v>
       </c>
@@ -2425,7 +2425,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>140</v>
       </c>
@@ -2442,7 +2442,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>140</v>
       </c>
@@ -2459,7 +2459,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>140</v>
       </c>
@@ -2476,7 +2476,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>140</v>
       </c>
@@ -2493,7 +2493,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>140</v>
       </c>
@@ -2510,7 +2510,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>140</v>
       </c>
@@ -2527,7 +2527,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>140</v>
       </c>
@@ -2544,7 +2544,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>140</v>
       </c>
@@ -2561,7 +2561,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>140</v>
       </c>
@@ -2578,7 +2578,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>160</v>
       </c>
@@ -2595,7 +2595,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>160</v>
       </c>
@@ -2612,7 +2612,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>160</v>
       </c>
@@ -2629,7 +2629,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>160</v>
       </c>
@@ -2646,7 +2646,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>160</v>
       </c>
@@ -2663,7 +2663,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>160</v>
       </c>
@@ -2680,7 +2680,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>160</v>
       </c>
@@ -2697,7 +2697,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>160</v>
       </c>
@@ -2714,7 +2714,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>160</v>
       </c>
@@ -2731,7 +2731,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>160</v>
       </c>
@@ -2748,7 +2748,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>160</v>
       </c>
@@ -2765,7 +2765,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>160</v>
       </c>
@@ -2782,7 +2782,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>160</v>
       </c>
@@ -2799,7 +2799,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>202</v>
       </c>
@@ -2816,7 +2816,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>202</v>
       </c>
@@ -2833,7 +2833,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>202</v>
       </c>
@@ -2850,7 +2850,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>202</v>
       </c>
@@ -2867,7 +2867,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>202</v>
       </c>
@@ -2884,7 +2884,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>202</v>
       </c>
@@ -2901,7 +2901,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>202</v>
       </c>
@@ -2918,7 +2918,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>202</v>
       </c>
@@ -2935,7 +2935,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>202</v>
       </c>
@@ -2952,7 +2952,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>202</v>
       </c>
@@ -2969,7 +2969,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>202</v>
       </c>
@@ -2986,7 +2986,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>202</v>
       </c>
@@ -3003,7 +3003,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>202</v>
       </c>
@@ -3020,7 +3020,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>202</v>
       </c>
@@ -3037,7 +3037,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>202</v>
       </c>
@@ -3054,7 +3054,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>202</v>
       </c>
@@ -3071,7 +3071,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>202</v>
       </c>
@@ -3088,7 +3088,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>202</v>
       </c>
@@ -3105,7 +3105,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>202</v>
       </c>
@@ -3122,7 +3122,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>202</v>
       </c>
@@ -3139,7 +3139,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>202</v>
       </c>
@@ -3156,7 +3156,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>202</v>
       </c>
@@ -3173,7 +3173,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>202</v>
       </c>
@@ -3193,7 +3193,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:E1 A3:E95 A2:D2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:E1 A3:E3 A2:D2 A5:E95 A4:D4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3201,9 +3201,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J229"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3235,7 +3235,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -3267,7 +3267,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -3299,7 +3299,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -3331,7 +3331,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -3363,7 +3363,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -3395,7 +3395,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -3427,7 +3427,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -3459,7 +3459,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -3491,7 +3491,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -3523,7 +3523,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -3555,7 +3555,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -3587,7 +3587,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -3619,7 +3619,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -3651,7 +3651,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -3683,7 +3683,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -3715,7 +3715,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -3747,7 +3747,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -3779,7 +3779,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -3811,7 +3811,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>5</v>
       </c>
@@ -3843,7 +3843,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -3875,7 +3875,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>5</v>
       </c>
@@ -3907,7 +3907,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>5</v>
       </c>
@@ -3939,7 +3939,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>5</v>
       </c>
@@ -3971,7 +3971,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -4003,7 +4003,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>5</v>
       </c>
@@ -4035,7 +4035,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -4067,7 +4067,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>5</v>
       </c>
@@ -4099,7 +4099,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -4131,7 +4131,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>5</v>
       </c>
@@ -4163,7 +4163,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -4195,7 +4195,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>5</v>
       </c>
@@ -4227,7 +4227,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>5</v>
       </c>
@@ -4259,7 +4259,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>5</v>
       </c>
@@ -4291,7 +4291,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>5</v>
       </c>
@@ -4323,7 +4323,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>5</v>
       </c>
@@ -4355,7 +4355,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>5</v>
       </c>
@@ -4387,7 +4387,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>5</v>
       </c>
@@ -4419,7 +4419,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>5</v>
       </c>
@@ -4451,7 +4451,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>5</v>
       </c>
@@ -4483,7 +4483,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>5</v>
       </c>
@@ -4515,7 +4515,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>5</v>
       </c>
@@ -4547,7 +4547,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>5</v>
       </c>
@@ -4579,7 +4579,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>5</v>
       </c>
@@ -4611,7 +4611,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>5</v>
       </c>
@@ -4643,7 +4643,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>5</v>
       </c>
@@ -4675,7 +4675,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>5</v>
       </c>
@@ -4707,7 +4707,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>5</v>
       </c>
@@ -4739,7 +4739,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>5</v>
       </c>
@@ -4771,7 +4771,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>5</v>
       </c>
@@ -4803,7 +4803,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>5</v>
       </c>
@@ -4835,7 +4835,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>5</v>
       </c>
@@ -4867,7 +4867,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>5</v>
       </c>
@@ -4899,7 +4899,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>5</v>
       </c>
@@ -4931,7 +4931,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>5</v>
       </c>
@@ -4963,7 +4963,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>5</v>
       </c>
@@ -4995,7 +4995,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>5</v>
       </c>
@@ -5027,7 +5027,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>5</v>
       </c>
@@ -5059,7 +5059,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>5</v>
       </c>
@@ -5091,7 +5091,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>5</v>
       </c>
@@ -5123,7 +5123,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>5</v>
       </c>
@@ -5155,7 +5155,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>5</v>
       </c>
@@ -5187,7 +5187,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>5</v>
       </c>
@@ -5219,7 +5219,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>5</v>
       </c>
@@ -5251,7 +5251,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>5</v>
       </c>
@@ -5283,7 +5283,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>5</v>
       </c>
@@ -5315,7 +5315,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>91</v>
       </c>
@@ -5347,7 +5347,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>91</v>
       </c>
@@ -5379,7 +5379,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>91</v>
       </c>
@@ -5411,7 +5411,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>91</v>
       </c>
@@ -5443,7 +5443,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>91</v>
       </c>
@@ -5475,7 +5475,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>91</v>
       </c>
@@ -5507,7 +5507,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>91</v>
       </c>
@@ -5539,7 +5539,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>91</v>
       </c>
@@ -5571,7 +5571,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>91</v>
       </c>
@@ -5603,7 +5603,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>91</v>
       </c>
@@ -5635,7 +5635,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>91</v>
       </c>
@@ -5667,7 +5667,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>91</v>
       </c>
@@ -5699,7 +5699,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>91</v>
       </c>
@@ -5731,7 +5731,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>91</v>
       </c>
@@ -5763,7 +5763,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>91</v>
       </c>
@@ -5795,7 +5795,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>91</v>
       </c>
@@ -5827,7 +5827,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>91</v>
       </c>
@@ -5859,7 +5859,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>91</v>
       </c>
@@ -5891,7 +5891,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>91</v>
       </c>
@@ -5923,7 +5923,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>91</v>
       </c>
@@ -5955,7 +5955,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>91</v>
       </c>
@@ -5987,7 +5987,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>91</v>
       </c>
@@ -6019,7 +6019,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>91</v>
       </c>
@@ -6051,7 +6051,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>91</v>
       </c>
@@ -6083,7 +6083,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>91</v>
       </c>
@@ -6115,7 +6115,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>91</v>
       </c>
@@ -6147,7 +6147,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>91</v>
       </c>
@@ -6179,7 +6179,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>91</v>
       </c>
@@ -6211,7 +6211,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>91</v>
       </c>
@@ -6243,7 +6243,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>91</v>
       </c>
@@ -6275,7 +6275,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>91</v>
       </c>
@@ -6307,7 +6307,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>91</v>
       </c>
@@ -6339,7 +6339,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>91</v>
       </c>
@@ -6371,7 +6371,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>91</v>
       </c>
@@ -6403,7 +6403,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>91</v>
       </c>
@@ -6435,7 +6435,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>91</v>
       </c>
@@ -6467,7 +6467,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>91</v>
       </c>
@@ -6499,7 +6499,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>91</v>
       </c>
@@ -6531,7 +6531,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="105" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>91</v>
       </c>
@@ -6563,7 +6563,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>91</v>
       </c>
@@ -6595,7 +6595,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="107" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>91</v>
       </c>
@@ -6627,7 +6627,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>91</v>
       </c>
@@ -6659,7 +6659,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>91</v>
       </c>
@@ -6691,7 +6691,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="110" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>91</v>
       </c>
@@ -6723,7 +6723,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="111" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>91</v>
       </c>
@@ -6755,7 +6755,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="112" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>91</v>
       </c>
@@ -6787,7 +6787,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>91</v>
       </c>
@@ -6819,7 +6819,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>91</v>
       </c>
@@ -6851,7 +6851,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="115" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>91</v>
       </c>
@@ -6883,7 +6883,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="116" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>91</v>
       </c>
@@ -6915,7 +6915,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>91</v>
       </c>
@@ -6947,7 +6947,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>91</v>
       </c>
@@ -6979,7 +6979,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="119" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>91</v>
       </c>
@@ -7011,7 +7011,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>91</v>
       </c>
@@ -7043,7 +7043,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>91</v>
       </c>
@@ -7075,7 +7075,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="122" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>91</v>
       </c>
@@ -7107,7 +7107,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>91</v>
       </c>
@@ -7139,7 +7139,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="124" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>91</v>
       </c>
@@ -7171,7 +7171,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="125" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>91</v>
       </c>
@@ -7203,7 +7203,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="126" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>91</v>
       </c>
@@ -7235,7 +7235,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="127" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>91</v>
       </c>
@@ -7267,7 +7267,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="128" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>140</v>
       </c>
@@ -7299,7 +7299,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>140</v>
       </c>
@@ -7331,7 +7331,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>140</v>
       </c>
@@ -7363,7 +7363,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="131" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>140</v>
       </c>
@@ -7395,7 +7395,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>140</v>
       </c>
@@ -7427,7 +7427,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>140</v>
       </c>
@@ -7459,7 +7459,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="134" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>140</v>
       </c>
@@ -7491,7 +7491,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>140</v>
       </c>
@@ -7523,7 +7523,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>140</v>
       </c>
@@ -7555,7 +7555,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="137" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>140</v>
       </c>
@@ -7587,7 +7587,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="138" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>140</v>
       </c>
@@ -7619,7 +7619,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="139" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>140</v>
       </c>
@@ -7651,7 +7651,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="140" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>140</v>
       </c>
@@ -7683,7 +7683,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="141" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>140</v>
       </c>
@@ -7715,7 +7715,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="142" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>140</v>
       </c>
@@ -7747,7 +7747,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="143" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>140</v>
       </c>
@@ -7779,7 +7779,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="144" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>140</v>
       </c>
@@ -7811,7 +7811,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>140</v>
       </c>
@@ -7843,7 +7843,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="146" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>140</v>
       </c>
@@ -7875,7 +7875,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>140</v>
       </c>
@@ -7907,7 +7907,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="148" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>140</v>
       </c>
@@ -7939,7 +7939,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="149" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>140</v>
       </c>
@@ -7971,7 +7971,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="150" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>140</v>
       </c>
@@ -8003,7 +8003,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="151" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>140</v>
       </c>
@@ -8035,7 +8035,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="152" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>140</v>
       </c>
@@ -8067,7 +8067,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="153" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>140</v>
       </c>
@@ -8099,7 +8099,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="154" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>140</v>
       </c>
@@ -8131,7 +8131,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="155" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>140</v>
       </c>
@@ -8163,7 +8163,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="156" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>140</v>
       </c>
@@ -8195,7 +8195,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="157" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>140</v>
       </c>
@@ -8227,7 +8227,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="158" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>160</v>
       </c>
@@ -8259,7 +8259,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="159" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>160</v>
       </c>
@@ -8291,7 +8291,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="160" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>160</v>
       </c>
@@ -8323,7 +8323,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="161" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>160</v>
       </c>
@@ -8355,7 +8355,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="162" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>160</v>
       </c>
@@ -8387,7 +8387,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="163" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>160</v>
       </c>
@@ -8419,7 +8419,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="164" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>160</v>
       </c>
@@ -8451,7 +8451,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="165" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>160</v>
       </c>
@@ -8483,7 +8483,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="166" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>160</v>
       </c>
@@ -8515,7 +8515,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="167" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>160</v>
       </c>
@@ -8547,7 +8547,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="168" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>160</v>
       </c>
@@ -8579,7 +8579,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="169" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>160</v>
       </c>
@@ -8611,7 +8611,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="170" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>160</v>
       </c>
@@ -8643,7 +8643,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="171" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>202</v>
       </c>
@@ -8675,7 +8675,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="172" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>202</v>
       </c>
@@ -8707,7 +8707,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="173" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>202</v>
       </c>
@@ -8739,7 +8739,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="174" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>202</v>
       </c>
@@ -8771,7 +8771,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="175" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>202</v>
       </c>
@@ -8803,7 +8803,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="176" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>202</v>
       </c>
@@ -8835,7 +8835,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="177" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>202</v>
       </c>
@@ -8867,7 +8867,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="178" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>202</v>
       </c>
@@ -8899,7 +8899,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="179" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>202</v>
       </c>
@@ -8931,7 +8931,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="180" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>202</v>
       </c>
@@ -8963,7 +8963,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="181" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>202</v>
       </c>
@@ -8995,7 +8995,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="182" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>202</v>
       </c>
@@ -9027,7 +9027,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="183" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>202</v>
       </c>
@@ -9059,7 +9059,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="184" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>202</v>
       </c>
@@ -9091,7 +9091,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="185" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>202</v>
       </c>
@@ -9123,7 +9123,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="186" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>202</v>
       </c>
@@ -9155,7 +9155,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="187" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>202</v>
       </c>
@@ -9187,7 +9187,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="188" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>202</v>
       </c>
@@ -9219,7 +9219,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="189" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>202</v>
       </c>
@@ -9251,7 +9251,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="190" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>202</v>
       </c>
@@ -9283,7 +9283,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="191" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>202</v>
       </c>
@@ -9315,7 +9315,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="192" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>202</v>
       </c>
@@ -9347,7 +9347,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="193" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>202</v>
       </c>
@@ -9379,7 +9379,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="194" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>202</v>
       </c>
@@ -9411,7 +9411,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="195" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>202</v>
       </c>
@@ -9443,7 +9443,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="196" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>202</v>
       </c>
@@ -9475,7 +9475,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="197" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>202</v>
       </c>
@@ -9507,7 +9507,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="198" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>202</v>
       </c>
@@ -9539,7 +9539,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="199" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>202</v>
       </c>
@@ -9571,7 +9571,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="200" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>202</v>
       </c>
@@ -9603,7 +9603,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="201" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>202</v>
       </c>
@@ -9635,7 +9635,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="202" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>202</v>
       </c>
@@ -9667,7 +9667,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="203" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>202</v>
       </c>
@@ -9699,7 +9699,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="204" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>202</v>
       </c>
@@ -9731,7 +9731,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="205" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>202</v>
       </c>
@@ -9763,7 +9763,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="206" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>202</v>
       </c>
@@ -9795,7 +9795,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="207" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>202</v>
       </c>
@@ -9827,7 +9827,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="208" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>202</v>
       </c>
@@ -9859,7 +9859,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="209" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>202</v>
       </c>
@@ -9891,7 +9891,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="210" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>202</v>
       </c>
@@ -9923,7 +9923,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="211" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>202</v>
       </c>
@@ -9955,7 +9955,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="212" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>202</v>
       </c>
@@ -9987,7 +9987,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="213" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>202</v>
       </c>
@@ -10019,7 +10019,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="214" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>202</v>
       </c>
@@ -10051,7 +10051,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="215" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>202</v>
       </c>
@@ -10083,7 +10083,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="216" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>202</v>
       </c>
@@ -10115,7 +10115,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="217" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>202</v>
       </c>
@@ -10147,7 +10147,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="218" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>202</v>
       </c>
@@ -10179,7 +10179,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="219" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>202</v>
       </c>
@@ -10211,7 +10211,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="220" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>202</v>
       </c>
@@ -10243,7 +10243,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="221" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>202</v>
       </c>
@@ -10275,7 +10275,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="222" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>202</v>
       </c>
@@ -10307,7 +10307,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="223" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>202</v>
       </c>
@@ -10339,7 +10339,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="224" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>202</v>
       </c>
@@ -10371,7 +10371,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="225" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>202</v>
       </c>
@@ -10403,7 +10403,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="226" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>202</v>
       </c>
@@ -10435,7 +10435,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="227" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>202</v>
       </c>
@@ -10467,7 +10467,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="228" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>202</v>
       </c>
@@ -10499,7 +10499,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="229" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>202</v>
       </c>
@@ -10542,9 +10542,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H553"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10570,7 +10570,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -10593,7 +10593,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -10616,7 +10616,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -10639,7 +10639,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -10662,7 +10662,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -10685,7 +10685,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -10708,7 +10708,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -10731,7 +10731,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -10754,7 +10754,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -10777,7 +10777,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -10800,7 +10800,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -10823,7 +10823,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -10846,7 +10846,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -10869,7 +10869,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -10892,7 +10892,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -10915,7 +10915,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -10938,7 +10938,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -10961,7 +10961,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -10984,7 +10984,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>5</v>
       </c>
@@ -11007,7 +11007,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -11030,7 +11030,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>5</v>
       </c>
@@ -11053,7 +11053,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>5</v>
       </c>
@@ -11076,7 +11076,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>5</v>
       </c>
@@ -11099,7 +11099,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -11122,7 +11122,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>5</v>
       </c>
@@ -11145,7 +11145,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -11168,7 +11168,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>5</v>
       </c>
@@ -11191,7 +11191,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -11214,7 +11214,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>5</v>
       </c>
@@ -11237,7 +11237,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -11260,7 +11260,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>5</v>
       </c>
@@ -11283,7 +11283,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>5</v>
       </c>
@@ -11306,7 +11306,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>5</v>
       </c>
@@ -11329,7 +11329,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>5</v>
       </c>
@@ -11352,7 +11352,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>5</v>
       </c>
@@ -11375,7 +11375,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>5</v>
       </c>
@@ -11398,7 +11398,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>5</v>
       </c>
@@ -11421,7 +11421,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>5</v>
       </c>
@@ -11444,7 +11444,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>5</v>
       </c>
@@ -11467,7 +11467,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>5</v>
       </c>
@@ -11490,7 +11490,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>5</v>
       </c>
@@ -11513,7 +11513,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>5</v>
       </c>
@@ -11536,7 +11536,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>5</v>
       </c>
@@ -11559,7 +11559,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>5</v>
       </c>
@@ -11582,7 +11582,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>5</v>
       </c>
@@ -11605,7 +11605,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>5</v>
       </c>
@@ -11628,7 +11628,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>5</v>
       </c>
@@ -11651,7 +11651,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>5</v>
       </c>
@@ -11674,7 +11674,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>5</v>
       </c>
@@ -11697,7 +11697,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>5</v>
       </c>
@@ -11720,7 +11720,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>5</v>
       </c>
@@ -11743,7 +11743,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>5</v>
       </c>
@@ -11766,7 +11766,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>5</v>
       </c>
@@ -11789,7 +11789,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>5</v>
       </c>
@@ -11812,7 +11812,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>5</v>
       </c>
@@ -11835,7 +11835,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>5</v>
       </c>
@@ -11858,7 +11858,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>5</v>
       </c>
@@ -11881,7 +11881,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>5</v>
       </c>
@@ -11904,7 +11904,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>5</v>
       </c>
@@ -11927,7 +11927,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>5</v>
       </c>
@@ -11950,7 +11950,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>5</v>
       </c>
@@ -11973,7 +11973,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>5</v>
       </c>
@@ -11996,7 +11996,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>5</v>
       </c>
@@ -12019,7 +12019,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>5</v>
       </c>
@@ -12042,7 +12042,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>5</v>
       </c>
@@ -12065,7 +12065,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>5</v>
       </c>
@@ -12088,7 +12088,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>5</v>
       </c>
@@ -12111,7 +12111,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>5</v>
       </c>
@@ -12134,7 +12134,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>5</v>
       </c>
@@ -12157,7 +12157,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>5</v>
       </c>
@@ -12180,7 +12180,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>5</v>
       </c>
@@ -12203,7 +12203,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>5</v>
       </c>
@@ -12226,7 +12226,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>5</v>
       </c>
@@ -12249,7 +12249,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>5</v>
       </c>
@@ -12272,7 +12272,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>5</v>
       </c>
@@ -12295,7 +12295,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>5</v>
       </c>
@@ -12318,7 +12318,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>5</v>
       </c>
@@ -12341,7 +12341,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>5</v>
       </c>
@@ -12364,7 +12364,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>5</v>
       </c>
@@ -12387,7 +12387,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>5</v>
       </c>
@@ -12410,7 +12410,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>5</v>
       </c>
@@ -12433,7 +12433,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>5</v>
       </c>
@@ -12456,7 +12456,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>5</v>
       </c>
@@ -12479,7 +12479,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>5</v>
       </c>
@@ -12502,7 +12502,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>5</v>
       </c>
@@ -12525,7 +12525,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>5</v>
       </c>
@@ -12548,7 +12548,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>5</v>
       </c>
@@ -12571,7 +12571,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>5</v>
       </c>
@@ -12594,7 +12594,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>5</v>
       </c>
@@ -12617,7 +12617,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>5</v>
       </c>
@@ -12640,7 +12640,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>5</v>
       </c>
@@ -12663,7 +12663,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>5</v>
       </c>
@@ -12686,7 +12686,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>5</v>
       </c>
@@ -12709,7 +12709,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>5</v>
       </c>
@@ -12732,7 +12732,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>5</v>
       </c>
@@ -12755,7 +12755,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>5</v>
       </c>
@@ -12778,7 +12778,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>5</v>
       </c>
@@ -12801,7 +12801,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>5</v>
       </c>
@@ -12824,7 +12824,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>5</v>
       </c>
@@ -12847,7 +12847,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>5</v>
       </c>
@@ -12870,7 +12870,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>5</v>
       </c>
@@ -12893,7 +12893,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>5</v>
       </c>
@@ -12916,7 +12916,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>5</v>
       </c>
@@ -12939,7 +12939,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>5</v>
       </c>
@@ -12962,7 +12962,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>5</v>
       </c>
@@ -12985,7 +12985,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>5</v>
       </c>
@@ -13008,7 +13008,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>5</v>
       </c>
@@ -13031,7 +13031,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>5</v>
       </c>
@@ -13054,7 +13054,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>5</v>
       </c>
@@ -13077,7 +13077,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="111" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>5</v>
       </c>
@@ -13100,7 +13100,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>5</v>
       </c>
@@ -13123,7 +13123,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="113" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>5</v>
       </c>
@@ -13146,7 +13146,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="114" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>5</v>
       </c>
@@ -13169,7 +13169,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>5</v>
       </c>
@@ -13192,7 +13192,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="116" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>5</v>
       </c>
@@ -13215,7 +13215,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>5</v>
       </c>
@@ -13238,7 +13238,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>5</v>
       </c>
@@ -13261,7 +13261,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>5</v>
       </c>
@@ -13284,7 +13284,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>5</v>
       </c>
@@ -13307,7 +13307,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>5</v>
       </c>
@@ -13330,7 +13330,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="122" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>5</v>
       </c>
@@ -13353,7 +13353,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>5</v>
       </c>
@@ -13376,7 +13376,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="124" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>5</v>
       </c>
@@ -13399,7 +13399,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="125" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>5</v>
       </c>
@@ -13422,7 +13422,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>5</v>
       </c>
@@ -13445,7 +13445,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="127" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>5</v>
       </c>
@@ -13468,7 +13468,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>5</v>
       </c>
@@ -13491,7 +13491,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>5</v>
       </c>
@@ -13514,7 +13514,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>5</v>
       </c>
@@ -13537,7 +13537,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>5</v>
       </c>
@@ -13560,7 +13560,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>5</v>
       </c>
@@ -13583,7 +13583,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>5</v>
       </c>
@@ -13606,7 +13606,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>5</v>
       </c>
@@ -13629,7 +13629,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="135" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>5</v>
       </c>
@@ -13652,7 +13652,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="136" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>5</v>
       </c>
@@ -13675,7 +13675,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>5</v>
       </c>
@@ -13698,7 +13698,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>5</v>
       </c>
@@ -13721,7 +13721,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="139" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>5</v>
       </c>
@@ -13744,7 +13744,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="140" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>91</v>
       </c>
@@ -13767,7 +13767,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="141" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>91</v>
       </c>
@@ -13790,7 +13790,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="142" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>91</v>
       </c>
@@ -13813,7 +13813,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>91</v>
       </c>
@@ -13836,7 +13836,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="144" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>91</v>
       </c>
@@ -13859,7 +13859,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="145" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>91</v>
       </c>
@@ -13882,7 +13882,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="146" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>91</v>
       </c>
@@ -13905,7 +13905,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="147" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>91</v>
       </c>
@@ -13928,7 +13928,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="148" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>91</v>
       </c>
@@ -13951,7 +13951,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="149" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>91</v>
       </c>
@@ -13974,7 +13974,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="150" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>91</v>
       </c>
@@ -13997,7 +13997,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="151" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>91</v>
       </c>
@@ -14020,7 +14020,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="152" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>91</v>
       </c>
@@ -14043,7 +14043,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="153" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>91</v>
       </c>
@@ -14066,7 +14066,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="154" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>91</v>
       </c>
@@ -14089,7 +14089,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="155" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>91</v>
       </c>
@@ -14112,7 +14112,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="156" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>91</v>
       </c>
@@ -14135,7 +14135,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="157" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>91</v>
       </c>
@@ -14158,7 +14158,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="158" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>91</v>
       </c>
@@ -14181,7 +14181,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="159" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>91</v>
       </c>
@@ -14204,7 +14204,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="160" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>91</v>
       </c>
@@ -14227,7 +14227,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="161" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>91</v>
       </c>
@@ -14250,7 +14250,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="162" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>91</v>
       </c>
@@ -14273,7 +14273,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="163" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>91</v>
       </c>
@@ -14296,7 +14296,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="164" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>91</v>
       </c>
@@ -14319,7 +14319,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="165" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>91</v>
       </c>
@@ -14342,7 +14342,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="166" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>91</v>
       </c>
@@ -14365,7 +14365,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="167" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>91</v>
       </c>
@@ -14388,7 +14388,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="168" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>91</v>
       </c>
@@ -14411,7 +14411,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="169" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>91</v>
       </c>
@@ -14434,7 +14434,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="170" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>91</v>
       </c>
@@ -14457,7 +14457,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="171" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>91</v>
       </c>
@@ -14480,7 +14480,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="172" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>91</v>
       </c>
@@ -14503,7 +14503,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="173" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>91</v>
       </c>
@@ -14526,7 +14526,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="174" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>91</v>
       </c>
@@ -14549,7 +14549,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="175" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>91</v>
       </c>
@@ -14572,7 +14572,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="176" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>91</v>
       </c>
@@ -14595,7 +14595,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="177" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>91</v>
       </c>
@@ -14618,7 +14618,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="178" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>91</v>
       </c>
@@ -14641,7 +14641,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="179" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>91</v>
       </c>
@@ -14664,7 +14664,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="180" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>91</v>
       </c>
@@ -14687,7 +14687,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="181" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>91</v>
       </c>
@@ -14710,7 +14710,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="182" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>91</v>
       </c>
@@ -14733,7 +14733,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="183" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>91</v>
       </c>
@@ -14756,7 +14756,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="184" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>91</v>
       </c>
@@ -14779,7 +14779,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="185" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>91</v>
       </c>
@@ -14802,7 +14802,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="186" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>91</v>
       </c>
@@ -14825,7 +14825,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="187" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>91</v>
       </c>
@@ -14848,7 +14848,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="188" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>91</v>
       </c>
@@ -14871,7 +14871,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="189" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>91</v>
       </c>
@@ -14894,7 +14894,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="190" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>91</v>
       </c>
@@ -14917,7 +14917,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="191" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>91</v>
       </c>
@@ -14940,7 +14940,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="192" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>91</v>
       </c>
@@ -14963,7 +14963,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="193" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>91</v>
       </c>
@@ -14986,7 +14986,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="194" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>91</v>
       </c>
@@ -15009,7 +15009,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="195" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>91</v>
       </c>
@@ -15032,7 +15032,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="196" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>91</v>
       </c>
@@ -15055,7 +15055,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="197" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>91</v>
       </c>
@@ -15078,7 +15078,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="198" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>91</v>
       </c>
@@ -15101,7 +15101,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="199" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>91</v>
       </c>
@@ -15124,7 +15124,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="200" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>91</v>
       </c>
@@ -15147,7 +15147,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="201" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>91</v>
       </c>
@@ -15170,7 +15170,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="202" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>91</v>
       </c>
@@ -15193,7 +15193,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="203" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>91</v>
       </c>
@@ -15216,7 +15216,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="204" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>91</v>
       </c>
@@ -15239,7 +15239,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="205" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>91</v>
       </c>
@@ -15262,7 +15262,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="206" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>91</v>
       </c>
@@ -15285,7 +15285,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="207" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>91</v>
       </c>
@@ -15308,7 +15308,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="208" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>91</v>
       </c>
@@ -15331,7 +15331,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="209" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>91</v>
       </c>
@@ -15354,7 +15354,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="210" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>91</v>
       </c>
@@ -15377,7 +15377,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="211" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>91</v>
       </c>
@@ -15400,7 +15400,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="212" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>91</v>
       </c>
@@ -15423,7 +15423,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="213" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>91</v>
       </c>
@@ -15446,7 +15446,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="214" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>91</v>
       </c>
@@ -15469,7 +15469,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="215" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>91</v>
       </c>
@@ -15492,7 +15492,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="216" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>91</v>
       </c>
@@ -15515,7 +15515,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="217" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>91</v>
       </c>
@@ -15538,7 +15538,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="218" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>91</v>
       </c>
@@ -15561,7 +15561,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="219" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>91</v>
       </c>
@@ -15584,7 +15584,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="220" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>91</v>
       </c>
@@ -15607,7 +15607,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="221" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>91</v>
       </c>
@@ -15630,7 +15630,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="222" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>91</v>
       </c>
@@ -15653,7 +15653,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="223" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>91</v>
       </c>
@@ -15676,7 +15676,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="224" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>91</v>
       </c>
@@ -15699,7 +15699,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="225" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>91</v>
       </c>
@@ -15722,7 +15722,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="226" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>91</v>
       </c>
@@ -15745,7 +15745,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="227" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>91</v>
       </c>
@@ -15768,7 +15768,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="228" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>91</v>
       </c>
@@ -15791,7 +15791,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="229" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>91</v>
       </c>
@@ -15814,7 +15814,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="230" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>91</v>
       </c>
@@ -15837,7 +15837,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="231" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>91</v>
       </c>
@@ -15860,7 +15860,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="232" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>91</v>
       </c>
@@ -15883,7 +15883,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="233" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>91</v>
       </c>
@@ -15906,7 +15906,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="234" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>91</v>
       </c>
@@ -15929,7 +15929,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="235" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>91</v>
       </c>
@@ -15952,7 +15952,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="236" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>91</v>
       </c>
@@ -15975,7 +15975,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="237" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>91</v>
       </c>
@@ -15998,7 +15998,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="238" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>91</v>
       </c>
@@ -16021,7 +16021,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="239" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>91</v>
       </c>
@@ -16044,7 +16044,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="240" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>91</v>
       </c>
@@ -16067,7 +16067,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="241" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>91</v>
       </c>
@@ -16090,7 +16090,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="242" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>91</v>
       </c>
@@ -16113,7 +16113,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="243" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>91</v>
       </c>
@@ -16136,7 +16136,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="244" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>91</v>
       </c>
@@ -16159,7 +16159,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="245" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>91</v>
       </c>
@@ -16182,7 +16182,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="246" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>91</v>
       </c>
@@ -16205,7 +16205,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="247" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>91</v>
       </c>
@@ -16228,7 +16228,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="248" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>91</v>
       </c>
@@ -16251,7 +16251,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="249" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>91</v>
       </c>
@@ -16274,7 +16274,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="250" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>91</v>
       </c>
@@ -16297,7 +16297,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="251" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>91</v>
       </c>
@@ -16320,7 +16320,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="252" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>91</v>
       </c>
@@ -16343,7 +16343,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="253" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>91</v>
       </c>
@@ -16366,7 +16366,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="254" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>91</v>
       </c>
@@ -16389,7 +16389,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="255" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>91</v>
       </c>
@@ -16412,7 +16412,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="256" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>91</v>
       </c>
@@ -16435,7 +16435,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="257" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>91</v>
       </c>
@@ -16458,7 +16458,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="258" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>91</v>
       </c>
@@ -16481,7 +16481,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="259" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>91</v>
       </c>
@@ -16504,7 +16504,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="260" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>91</v>
       </c>
@@ -16527,7 +16527,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="261" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>91</v>
       </c>
@@ -16550,7 +16550,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="262" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>91</v>
       </c>
@@ -16573,7 +16573,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="263" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>91</v>
       </c>
@@ -16596,7 +16596,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="264" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>91</v>
       </c>
@@ -16619,7 +16619,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="265" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>91</v>
       </c>
@@ -16642,7 +16642,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="266" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>91</v>
       </c>
@@ -16665,7 +16665,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="267" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>91</v>
       </c>
@@ -16688,7 +16688,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="268" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>91</v>
       </c>
@@ -16711,7 +16711,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="269" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>91</v>
       </c>
@@ -16734,7 +16734,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="270" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>91</v>
       </c>
@@ -16757,7 +16757,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="271" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>91</v>
       </c>
@@ -16780,7 +16780,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="272" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>91</v>
       </c>
@@ -16803,7 +16803,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="273" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>91</v>
       </c>
@@ -16826,7 +16826,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="274" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>91</v>
       </c>
@@ -16849,7 +16849,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="275" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>91</v>
       </c>
@@ -16872,7 +16872,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="276" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>91</v>
       </c>
@@ -16895,7 +16895,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="277" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>91</v>
       </c>
@@ -16918,7 +16918,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="278" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>91</v>
       </c>
@@ -16941,7 +16941,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="279" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>91</v>
       </c>
@@ -16964,7 +16964,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="280" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>91</v>
       </c>
@@ -16987,7 +16987,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="281" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>91</v>
       </c>
@@ -17010,7 +17010,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="282" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>91</v>
       </c>
@@ -17033,7 +17033,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="283" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>91</v>
       </c>
@@ -17056,7 +17056,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="284" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>140</v>
       </c>
@@ -17079,7 +17079,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="285" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>140</v>
       </c>
@@ -17102,7 +17102,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="286" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>140</v>
       </c>
@@ -17125,7 +17125,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="287" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>140</v>
       </c>
@@ -17148,7 +17148,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="288" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>140</v>
       </c>
@@ -17171,7 +17171,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="289" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>140</v>
       </c>
@@ -17194,7 +17194,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="290" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>140</v>
       </c>
@@ -17217,7 +17217,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="291" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>140</v>
       </c>
@@ -17240,7 +17240,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="292" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>140</v>
       </c>
@@ -17263,7 +17263,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="293" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>140</v>
       </c>
@@ -17286,7 +17286,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="294" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>140</v>
       </c>
@@ -17309,7 +17309,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="295" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>140</v>
       </c>
@@ -17332,7 +17332,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="296" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>140</v>
       </c>
@@ -17355,7 +17355,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="297" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>140</v>
       </c>
@@ -17378,7 +17378,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="298" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>140</v>
       </c>
@@ -17401,7 +17401,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="299" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>140</v>
       </c>
@@ -17424,7 +17424,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="300" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>140</v>
       </c>
@@ -17447,7 +17447,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="301" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>140</v>
       </c>
@@ -17470,7 +17470,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="302" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>140</v>
       </c>
@@ -17493,7 +17493,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="303" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>140</v>
       </c>
@@ -17516,7 +17516,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="304" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>140</v>
       </c>
@@ -17539,7 +17539,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="305" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>140</v>
       </c>
@@ -17562,7 +17562,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="306" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>140</v>
       </c>
@@ -17585,7 +17585,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="307" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>140</v>
       </c>
@@ -17608,7 +17608,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="308" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>140</v>
       </c>
@@ -17631,7 +17631,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="309" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>140</v>
       </c>
@@ -17654,7 +17654,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="310" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>140</v>
       </c>
@@ -17677,7 +17677,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="311" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>140</v>
       </c>
@@ -17700,7 +17700,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="312" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>140</v>
       </c>
@@ -17723,7 +17723,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="313" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>140</v>
       </c>
@@ -17746,7 +17746,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="314" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>140</v>
       </c>
@@ -17769,7 +17769,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="315" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>140</v>
       </c>
@@ -17792,7 +17792,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="316" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>140</v>
       </c>
@@ -17815,7 +17815,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="317" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>140</v>
       </c>
@@ -17838,7 +17838,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="318" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>140</v>
       </c>
@@ -17861,7 +17861,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="319" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>140</v>
       </c>
@@ -17884,7 +17884,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="320" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>140</v>
       </c>
@@ -17907,7 +17907,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="321" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>140</v>
       </c>
@@ -17930,7 +17930,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="322" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>140</v>
       </c>
@@ -17953,7 +17953,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="323" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>140</v>
       </c>
@@ -17976,7 +17976,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="324" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>140</v>
       </c>
@@ -17999,7 +17999,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="325" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>140</v>
       </c>
@@ -18022,7 +18022,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="326" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>140</v>
       </c>
@@ -18045,7 +18045,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="327" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>140</v>
       </c>
@@ -18068,7 +18068,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="328" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>140</v>
       </c>
@@ -18091,7 +18091,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="329" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>140</v>
       </c>
@@ -18114,7 +18114,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="330" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>140</v>
       </c>
@@ -18137,7 +18137,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="331" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>140</v>
       </c>
@@ -18160,7 +18160,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="332" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>140</v>
       </c>
@@ -18183,7 +18183,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="333" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>140</v>
       </c>
@@ -18206,7 +18206,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="334" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>140</v>
       </c>
@@ -18229,7 +18229,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="335" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>140</v>
       </c>
@@ -18252,7 +18252,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="336" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>140</v>
       </c>
@@ -18275,7 +18275,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="337" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>140</v>
       </c>
@@ -18298,7 +18298,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="338" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>160</v>
       </c>
@@ -18321,7 +18321,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="339" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>160</v>
       </c>
@@ -18344,7 +18344,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="340" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>160</v>
       </c>
@@ -18367,7 +18367,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="341" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>160</v>
       </c>
@@ -18390,7 +18390,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="342" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>160</v>
       </c>
@@ -18413,7 +18413,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="343" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>160</v>
       </c>
@@ -18436,7 +18436,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="344" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>160</v>
       </c>
@@ -18459,7 +18459,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="345" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>160</v>
       </c>
@@ -18482,7 +18482,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="346" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>160</v>
       </c>
@@ -18505,7 +18505,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="347" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>160</v>
       </c>
@@ -18528,7 +18528,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="348" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>160</v>
       </c>
@@ -18551,7 +18551,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="349" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>160</v>
       </c>
@@ -18574,7 +18574,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="350" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>160</v>
       </c>
@@ -18597,7 +18597,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="351" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>160</v>
       </c>
@@ -18620,7 +18620,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="352" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>160</v>
       </c>
@@ -18643,7 +18643,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="353" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>160</v>
       </c>
@@ -18666,7 +18666,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="354" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>160</v>
       </c>
@@ -18689,7 +18689,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="355" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>160</v>
       </c>
@@ -18712,7 +18712,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="356" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>160</v>
       </c>
@@ -18735,7 +18735,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="357" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>160</v>
       </c>
@@ -18758,7 +18758,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="358" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>160</v>
       </c>
@@ -18781,7 +18781,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="359" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>160</v>
       </c>
@@ -18804,7 +18804,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="360" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>160</v>
       </c>
@@ -18827,7 +18827,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="361" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>160</v>
       </c>
@@ -18850,7 +18850,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="362" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>160</v>
       </c>
@@ -18873,7 +18873,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="363" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>160</v>
       </c>
@@ -18896,7 +18896,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="364" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>160</v>
       </c>
@@ -18919,7 +18919,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="365" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>160</v>
       </c>
@@ -18942,7 +18942,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="366" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>160</v>
       </c>
@@ -18965,7 +18965,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="367" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>160</v>
       </c>
@@ -18988,7 +18988,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="368" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>160</v>
       </c>
@@ -19011,7 +19011,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="369" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>160</v>
       </c>
@@ -19034,7 +19034,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="370" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>160</v>
       </c>
@@ -19057,7 +19057,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="371" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>160</v>
       </c>
@@ -19080,7 +19080,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="372" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>160</v>
       </c>
@@ -19103,7 +19103,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="373" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>160</v>
       </c>
@@ -19126,7 +19126,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="374" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>160</v>
       </c>
@@ -19149,7 +19149,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="375" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>160</v>
       </c>
@@ -19172,7 +19172,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="376" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>160</v>
       </c>
@@ -19195,7 +19195,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="377" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>160</v>
       </c>
@@ -19218,7 +19218,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="378" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>160</v>
       </c>
@@ -19241,7 +19241,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="379" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>160</v>
       </c>
@@ -19264,7 +19264,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="380" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>160</v>
       </c>
@@ -19287,7 +19287,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="381" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>160</v>
       </c>
@@ -19310,7 +19310,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="382" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>160</v>
       </c>
@@ -19333,7 +19333,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="383" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>160</v>
       </c>
@@ -19356,7 +19356,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="384" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>160</v>
       </c>
@@ -19379,7 +19379,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="385" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>160</v>
       </c>
@@ -19402,7 +19402,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="386" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>160</v>
       </c>
@@ -19425,7 +19425,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="387" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>160</v>
       </c>
@@ -19448,7 +19448,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="388" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>160</v>
       </c>
@@ -19471,7 +19471,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="389" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>160</v>
       </c>
@@ -19494,7 +19494,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="390" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>160</v>
       </c>
@@ -19517,7 +19517,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="391" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>160</v>
       </c>
@@ -19540,7 +19540,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="392" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>160</v>
       </c>
@@ -19563,7 +19563,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="393" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>160</v>
       </c>
@@ -19586,7 +19586,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="394" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>160</v>
       </c>
@@ -19609,7 +19609,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="395" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>160</v>
       </c>
@@ -19632,7 +19632,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="396" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>160</v>
       </c>
@@ -19655,7 +19655,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="397" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>160</v>
       </c>
@@ -19678,7 +19678,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="398" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>160</v>
       </c>
@@ -19701,7 +19701,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="399" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>160</v>
       </c>
@@ -19724,7 +19724,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="400" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>160</v>
       </c>
@@ -19747,7 +19747,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="401" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>160</v>
       </c>
@@ -19770,7 +19770,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="402" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>160</v>
       </c>
@@ -19793,7 +19793,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="403" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>160</v>
       </c>
@@ -19816,7 +19816,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="404" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>160</v>
       </c>
@@ -19839,7 +19839,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="405" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>160</v>
       </c>
@@ -19862,7 +19862,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="406" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>160</v>
       </c>
@@ -19885,7 +19885,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="407" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>160</v>
       </c>
@@ -19908,7 +19908,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="408" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>160</v>
       </c>
@@ -19931,7 +19931,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="409" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>160</v>
       </c>
@@ -19954,7 +19954,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="410" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>160</v>
       </c>
@@ -19977,7 +19977,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="411" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>160</v>
       </c>
@@ -20000,7 +20000,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="412" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>160</v>
       </c>
@@ -20023,7 +20023,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="413" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>160</v>
       </c>
@@ -20046,7 +20046,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="414" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>160</v>
       </c>
@@ -20069,7 +20069,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="415" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>160</v>
       </c>
@@ -20092,7 +20092,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="416" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>202</v>
       </c>
@@ -20115,7 +20115,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="417" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>202</v>
       </c>
@@ -20138,7 +20138,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="418" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>202</v>
       </c>
@@ -20161,7 +20161,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="419" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>202</v>
       </c>
@@ -20184,7 +20184,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="420" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>202</v>
       </c>
@@ -20207,7 +20207,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="421" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>202</v>
       </c>
@@ -20230,7 +20230,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="422" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>202</v>
       </c>
@@ -20253,7 +20253,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="423" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>202</v>
       </c>
@@ -20276,7 +20276,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="424" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>202</v>
       </c>
@@ -20299,7 +20299,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="425" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>202</v>
       </c>
@@ -20322,7 +20322,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="426" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>202</v>
       </c>
@@ -20345,7 +20345,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="427" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>202</v>
       </c>
@@ -20368,7 +20368,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="428" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>202</v>
       </c>
@@ -20391,7 +20391,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="429" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>202</v>
       </c>
@@ -20414,7 +20414,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="430" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>202</v>
       </c>
@@ -20437,7 +20437,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="431" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>202</v>
       </c>
@@ -20460,7 +20460,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="432" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>202</v>
       </c>
@@ -20483,7 +20483,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="433" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>202</v>
       </c>
@@ -20506,7 +20506,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="434" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>202</v>
       </c>
@@ -20529,7 +20529,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="435" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>202</v>
       </c>
@@ -20552,7 +20552,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="436" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>202</v>
       </c>
@@ -20575,7 +20575,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="437" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>202</v>
       </c>
@@ -20598,7 +20598,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="438" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>202</v>
       </c>
@@ -20621,7 +20621,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="439" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>202</v>
       </c>
@@ -20644,7 +20644,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="440" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>202</v>
       </c>
@@ -20667,7 +20667,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="441" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>202</v>
       </c>
@@ -20690,7 +20690,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="442" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>202</v>
       </c>
@@ -20713,7 +20713,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="443" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>202</v>
       </c>
@@ -20736,7 +20736,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="444" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>202</v>
       </c>
@@ -20759,7 +20759,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="445" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>202</v>
       </c>
@@ -20782,7 +20782,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="446" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>202</v>
       </c>
@@ -20805,7 +20805,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="447" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>202</v>
       </c>
@@ -20828,7 +20828,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="448" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>202</v>
       </c>
@@ -20851,7 +20851,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="449" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>202</v>
       </c>
@@ -20874,7 +20874,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="450" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>202</v>
       </c>
@@ -20897,7 +20897,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="451" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>202</v>
       </c>
@@ -20920,7 +20920,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="452" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>202</v>
       </c>
@@ -20943,7 +20943,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="453" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>202</v>
       </c>
@@ -20966,7 +20966,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="454" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>202</v>
       </c>
@@ -20989,7 +20989,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="455" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>202</v>
       </c>
@@ -21012,7 +21012,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="456" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>202</v>
       </c>
@@ -21035,7 +21035,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="457" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>202</v>
       </c>
@@ -21058,7 +21058,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="458" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>202</v>
       </c>
@@ -21081,7 +21081,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="459" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>202</v>
       </c>
@@ -21104,7 +21104,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="460" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>202</v>
       </c>
@@ -21127,7 +21127,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="461" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>202</v>
       </c>
@@ -21150,7 +21150,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="462" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>202</v>
       </c>
@@ -21173,7 +21173,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="463" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>202</v>
       </c>
@@ -21196,7 +21196,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="464" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>202</v>
       </c>
@@ -21219,7 +21219,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="465" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>202</v>
       </c>
@@ -21242,7 +21242,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="466" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>202</v>
       </c>
@@ -21265,7 +21265,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="467" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>202</v>
       </c>
@@ -21288,7 +21288,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="468" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>202</v>
       </c>
@@ -21311,7 +21311,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="469" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
         <v>202</v>
       </c>
@@ -21334,7 +21334,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="470" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
         <v>202</v>
       </c>
@@ -21357,7 +21357,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="471" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>202</v>
       </c>
@@ -21380,7 +21380,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="472" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>202</v>
       </c>
@@ -21403,7 +21403,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="473" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>202</v>
       </c>
@@ -21426,7 +21426,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="474" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>202</v>
       </c>
@@ -21449,7 +21449,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="475" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>202</v>
       </c>
@@ -21472,7 +21472,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="476" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>202</v>
       </c>
@@ -21495,7 +21495,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="477" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>202</v>
       </c>
@@ -21518,7 +21518,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="478" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>202</v>
       </c>
@@ -21541,7 +21541,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="479" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>202</v>
       </c>
@@ -21564,7 +21564,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="480" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>202</v>
       </c>
@@ -21587,7 +21587,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="481" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>202</v>
       </c>
@@ -21610,7 +21610,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="482" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>202</v>
       </c>
@@ -21633,7 +21633,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="483" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>202</v>
       </c>
@@ -21656,7 +21656,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="484" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>202</v>
       </c>
@@ -21679,7 +21679,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="485" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>202</v>
       </c>
@@ -21702,7 +21702,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="486" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>202</v>
       </c>
@@ -21725,7 +21725,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="487" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
         <v>202</v>
       </c>
@@ -21748,7 +21748,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="488" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
         <v>202</v>
       </c>
@@ -21771,7 +21771,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="489" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
         <v>202</v>
       </c>
@@ -21794,7 +21794,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="490" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
         <v>202</v>
       </c>
@@ -21817,7 +21817,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="491" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
         <v>202</v>
       </c>
@@ -21840,7 +21840,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="492" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
         <v>202</v>
       </c>
@@ -21863,7 +21863,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="493" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
         <v>202</v>
       </c>
@@ -21886,7 +21886,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="494" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
         <v>202</v>
       </c>
@@ -21909,7 +21909,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="495" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
         <v>202</v>
       </c>
@@ -21932,7 +21932,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="496" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
         <v>202</v>
       </c>
@@ -21955,7 +21955,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="497" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
         <v>202</v>
       </c>
@@ -21978,7 +21978,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="498" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
         <v>202</v>
       </c>
@@ -22001,7 +22001,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="499" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
         <v>202</v>
       </c>
@@ -22024,7 +22024,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="500" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
         <v>202</v>
       </c>
@@ -22047,7 +22047,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="501" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
         <v>202</v>
       </c>
@@ -22070,7 +22070,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="502" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
         <v>202</v>
       </c>
@@ -22093,7 +22093,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="503" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
         <v>202</v>
       </c>
@@ -22116,7 +22116,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="504" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
         <v>202</v>
       </c>
@@ -22139,7 +22139,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="505" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
         <v>202</v>
       </c>
@@ -22162,7 +22162,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="506" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
         <v>202</v>
       </c>
@@ -22185,7 +22185,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="507" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
         <v>202</v>
       </c>
@@ -22208,7 +22208,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="508" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
         <v>202</v>
       </c>
@@ -22231,7 +22231,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="509" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
         <v>202</v>
       </c>
@@ -22254,7 +22254,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="510" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
         <v>202</v>
       </c>
@@ -22277,7 +22277,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="511" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
         <v>202</v>
       </c>
@@ -22300,7 +22300,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="512" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
         <v>202</v>
       </c>
@@ -22323,7 +22323,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="513" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
         <v>202</v>
       </c>
@@ -22346,7 +22346,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="514" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
         <v>202</v>
       </c>
@@ -22369,7 +22369,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="515" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
         <v>202</v>
       </c>
@@ -22392,7 +22392,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="516" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
         <v>202</v>
       </c>
@@ -22415,7 +22415,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="517" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
         <v>202</v>
       </c>
@@ -22438,7 +22438,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="518" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
         <v>202</v>
       </c>
@@ -22461,7 +22461,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="519" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
         <v>202</v>
       </c>
@@ -22484,7 +22484,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="520" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
         <v>202</v>
       </c>
@@ -22507,7 +22507,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="521" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
         <v>202</v>
       </c>
@@ -22530,7 +22530,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="522" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
         <v>202</v>
       </c>
@@ -22553,7 +22553,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="523" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
         <v>202</v>
       </c>
@@ -22576,7 +22576,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="524" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
         <v>202</v>
       </c>
@@ -22599,7 +22599,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="525" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
         <v>202</v>
       </c>
@@ -22622,7 +22622,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="526" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
         <v>202</v>
       </c>
@@ -22645,7 +22645,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="527" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
         <v>202</v>
       </c>
@@ -22668,7 +22668,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="528" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
         <v>202</v>
       </c>
@@ -22691,7 +22691,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="529" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
         <v>202</v>
       </c>
@@ -22714,7 +22714,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="530" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
         <v>202</v>
       </c>
@@ -22737,7 +22737,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="531" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
         <v>202</v>
       </c>
@@ -22760,7 +22760,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="532" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
         <v>202</v>
       </c>
@@ -22783,7 +22783,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="533" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
         <v>202</v>
       </c>
@@ -22806,7 +22806,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="534" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
         <v>202</v>
       </c>
@@ -22829,7 +22829,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="535" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
         <v>202</v>
       </c>
@@ -22852,7 +22852,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="536" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
         <v>202</v>
       </c>
@@ -22875,7 +22875,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="537" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
         <v>202</v>
       </c>
@@ -22898,7 +22898,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="538" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
         <v>202</v>
       </c>
@@ -22921,7 +22921,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="539" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
         <v>202</v>
       </c>
@@ -22944,7 +22944,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="540" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
         <v>202</v>
       </c>
@@ -22967,7 +22967,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="541" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
         <v>202</v>
       </c>
@@ -22990,7 +22990,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="542" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
         <v>202</v>
       </c>
@@ -23013,7 +23013,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="543" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
         <v>202</v>
       </c>
@@ -23036,7 +23036,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="544" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
         <v>202</v>
       </c>
@@ -23059,7 +23059,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="545" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
         <v>202</v>
       </c>
@@ -23082,7 +23082,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="546" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
         <v>202</v>
       </c>
@@ -23105,7 +23105,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="547" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
         <v>202</v>
       </c>
@@ -23128,7 +23128,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="548" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
         <v>202</v>
       </c>
@@ -23151,7 +23151,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="549" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
         <v>202</v>
       </c>
@@ -23174,7 +23174,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="550" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
         <v>202</v>
       </c>
@@ -23197,7 +23197,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="551" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
         <v>202</v>
       </c>
@@ -23220,7 +23220,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="552" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
         <v>202</v>
       </c>
@@ -23243,7 +23243,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="553" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
         <v>202</v>
       </c>
@@ -23277,7 +23277,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.796875" customWidth="1"/>
     <col min="2" max="2" width="38.796875" customWidth="1"/>
@@ -23287,7 +23287,7 @@
     <col min="6" max="6" width="12.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -23307,7 +23307,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -23327,7 +23327,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -23347,7 +23347,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -23367,7 +23367,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -23387,7 +23387,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -23407,7 +23407,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -23427,7 +23427,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -23447,7 +23447,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -23467,7 +23467,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>5</v>
       </c>
